--- a/experiment_stimuli/Block7.xlsx
+++ b/experiment_stimuli/Block7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frances\Desktop\sdt\experiment_stimuli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F724AD-0D57-453F-94E3-BDC175491C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC3F008-0029-4FF5-BF4C-43A1AFC06B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1830" yWindow="1830" windowWidth="17172" windowHeight="11064" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9414" yWindow="1818" windowWidth="17172" windowHeight="11064" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -88,13 +88,13 @@
     <t>The candidate was a liberal trumpet.</t>
   </si>
   <si>
-    <t>His eyes were two whirlpools.</t>
-  </si>
-  <si>
     <t>The job was a career lever.</t>
   </si>
   <si>
     <t>correct_answer</t>
+  </si>
+  <si>
+    <t>His eyes were two blue whirlpools.</t>
   </si>
 </sst>
 </file>
@@ -380,7 +380,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -629,7 +629,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>6</v>
@@ -646,7 +646,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>6</v>
